--- a/resources/Z517/spc_sheet_oos_decoration.xlsx
+++ b/resources/Z517/spc_sheet_oos_decoration.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
   <si>
     <t>factory</t>
   </si>
@@ -53,12 +53,39 @@
   </si>
   <si>
     <t>flag</t>
+  </si>
+  <si>
+    <t>ARRAY</t>
+  </si>
+  <si>
+    <t>Z517</t>
+  </si>
+  <si>
+    <t>15620</t>
+  </si>
+  <si>
+    <t>TDSUM</t>
+  </si>
+  <si>
+    <t>L3Z66600S05</t>
+  </si>
+  <si>
+    <t>L3Z66600S10</t>
+  </si>
+  <si>
+    <t>L3Z66600S29</t>
+  </si>
+  <si>
+    <t>USL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -111,11 +138,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -410,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -454,6 +482,120 @@
         <v>12</v>
       </c>
     </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46224.50951388889</v>
+      </c>
+      <c r="G2">
+        <v>2710</v>
+      </c>
+      <c r="H2">
+        <v>2710</v>
+      </c>
+      <c r="I2">
+        <v>2710</v>
+      </c>
+      <c r="J2">
+        <v>2630</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="2">
+        <v>46224.52693287037</v>
+      </c>
+      <c r="G3">
+        <v>2849</v>
+      </c>
+      <c r="H3">
+        <v>2849</v>
+      </c>
+      <c r="I3">
+        <v>2849</v>
+      </c>
+      <c r="J3">
+        <v>2630</v>
+      </c>
+      <c r="L3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46224.58733796296</v>
+      </c>
+      <c r="G4">
+        <v>2828</v>
+      </c>
+      <c r="H4">
+        <v>2828</v>
+      </c>
+      <c r="I4">
+        <v>2828</v>
+      </c>
+      <c r="J4">
+        <v>2630</v>
+      </c>
+      <c r="L4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/resources/Z517/spc_sheet_oos_decoration.xlsx
+++ b/resources/Z517/spc_sheet_oos_decoration.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>factory</t>
   </si>
@@ -53,39 +53,12 @@
   </si>
   <si>
     <t>flag</t>
-  </si>
-  <si>
-    <t>ARRAY</t>
-  </si>
-  <si>
-    <t>Z517</t>
-  </si>
-  <si>
-    <t>15620</t>
-  </si>
-  <si>
-    <t>TDSUM</t>
-  </si>
-  <si>
-    <t>L3Z66600S05</t>
-  </si>
-  <si>
-    <t>L3Z66600S10</t>
-  </si>
-  <si>
-    <t>L3Z66600S29</t>
-  </si>
-  <si>
-    <t>USL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -138,12 +111,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -482,120 +454,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="2">
-        <v>46224.50951388889</v>
-      </c>
-      <c r="G2">
-        <v>2710</v>
-      </c>
-      <c r="H2">
-        <v>2710</v>
-      </c>
-      <c r="I2">
-        <v>2710</v>
-      </c>
-      <c r="J2">
-        <v>2630</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="2">
-        <v>46224.52693287037</v>
-      </c>
-      <c r="G3">
-        <v>2849</v>
-      </c>
-      <c r="H3">
-        <v>2849</v>
-      </c>
-      <c r="I3">
-        <v>2849</v>
-      </c>
-      <c r="J3">
-        <v>2630</v>
-      </c>
-      <c r="L3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="2">
-        <v>46224.58733796296</v>
-      </c>
-      <c r="G4">
-        <v>2828</v>
-      </c>
-      <c r="H4">
-        <v>2828</v>
-      </c>
-      <c r="I4">
-        <v>2828</v>
-      </c>
-      <c r="J4">
-        <v>2630</v>
-      </c>
-      <c r="L4" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" t="b">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/resources/Z517/spc_sheet_oos_decoration.xlsx
+++ b/resources/Z517/spc_sheet_oos_decoration.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="28">
   <si>
     <t>factory</t>
   </si>
@@ -53,12 +53,60 @@
   </si>
   <si>
     <t>flag</t>
+  </si>
+  <si>
+    <t>ARRAY</t>
+  </si>
+  <si>
+    <t>Z517</t>
+  </si>
+  <si>
+    <t>11620</t>
+  </si>
+  <si>
+    <t>12620</t>
+  </si>
+  <si>
+    <t>13620</t>
+  </si>
+  <si>
+    <t>18620</t>
+  </si>
+  <si>
+    <t>TDSUM</t>
+  </si>
+  <si>
+    <t>L3Z66700U16</t>
+  </si>
+  <si>
+    <t>L3Z66700S19</t>
+  </si>
+  <si>
+    <t>L3Z66700S27</t>
+  </si>
+  <si>
+    <t>L3Z66700S28</t>
+  </si>
+  <si>
+    <t>L3Z66700S29</t>
+  </si>
+  <si>
+    <t>L3Z66700D22</t>
+  </si>
+  <si>
+    <t>L3Z66700103</t>
+  </si>
+  <si>
+    <t>USL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -111,11 +159,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -410,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -454,6 +503,272 @@
         <v>12</v>
       </c>
     </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46238.35493055556</v>
+      </c>
+      <c r="G2">
+        <v>657</v>
+      </c>
+      <c r="H2">
+        <v>657</v>
+      </c>
+      <c r="I2">
+        <v>657</v>
+      </c>
+      <c r="J2">
+        <v>618</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="2">
+        <v>46240.52037037037</v>
+      </c>
+      <c r="G3">
+        <v>1722</v>
+      </c>
+      <c r="H3">
+        <v>1722</v>
+      </c>
+      <c r="I3">
+        <v>1722</v>
+      </c>
+      <c r="J3">
+        <v>770</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46240.54273148148</v>
+      </c>
+      <c r="G4">
+        <v>1922</v>
+      </c>
+      <c r="H4">
+        <v>1922</v>
+      </c>
+      <c r="I4">
+        <v>1922</v>
+      </c>
+      <c r="J4">
+        <v>770</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="2">
+        <v>46240.545</v>
+      </c>
+      <c r="G5">
+        <v>4837</v>
+      </c>
+      <c r="H5">
+        <v>4837</v>
+      </c>
+      <c r="I5">
+        <v>4837</v>
+      </c>
+      <c r="J5">
+        <v>770</v>
+      </c>
+      <c r="L5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="2">
+        <v>46240.54693287037</v>
+      </c>
+      <c r="G6">
+        <v>1047</v>
+      </c>
+      <c r="H6">
+        <v>1047</v>
+      </c>
+      <c r="I6">
+        <v>1047</v>
+      </c>
+      <c r="J6">
+        <v>770</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46239.97922453703</v>
+      </c>
+      <c r="G7">
+        <v>1683</v>
+      </c>
+      <c r="H7">
+        <v>1683</v>
+      </c>
+      <c r="I7">
+        <v>1683</v>
+      </c>
+      <c r="J7">
+        <v>1308</v>
+      </c>
+      <c r="L7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="2">
+        <v>46240.96769675926</v>
+      </c>
+      <c r="G8">
+        <v>5000</v>
+      </c>
+      <c r="H8">
+        <v>5000</v>
+      </c>
+      <c r="I8">
+        <v>5000</v>
+      </c>
+      <c r="J8">
+        <v>2630</v>
+      </c>
+      <c r="L8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/resources/Z517/spc_sheet_oos_decoration.xlsx
+++ b/resources/Z517/spc_sheet_oos_decoration.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>factory</t>
   </si>
@@ -53,60 +53,12 @@
   </si>
   <si>
     <t>flag</t>
-  </si>
-  <si>
-    <t>ARRAY</t>
-  </si>
-  <si>
-    <t>Z517</t>
-  </si>
-  <si>
-    <t>11620</t>
-  </si>
-  <si>
-    <t>12620</t>
-  </si>
-  <si>
-    <t>13620</t>
-  </si>
-  <si>
-    <t>18620</t>
-  </si>
-  <si>
-    <t>TDSUM</t>
-  </si>
-  <si>
-    <t>L3Z66700U16</t>
-  </si>
-  <si>
-    <t>L3Z66700S19</t>
-  </si>
-  <si>
-    <t>L3Z66700S27</t>
-  </si>
-  <si>
-    <t>L3Z66700S28</t>
-  </si>
-  <si>
-    <t>L3Z66700S29</t>
-  </si>
-  <si>
-    <t>L3Z66700D22</t>
-  </si>
-  <si>
-    <t>L3Z66700103</t>
-  </si>
-  <si>
-    <t>USL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -159,12 +111,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -459,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -503,272 +454,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="2">
-        <v>46238.35493055556</v>
-      </c>
-      <c r="G2">
-        <v>657</v>
-      </c>
-      <c r="H2">
-        <v>657</v>
-      </c>
-      <c r="I2">
-        <v>657</v>
-      </c>
-      <c r="J2">
-        <v>618</v>
-      </c>
-      <c r="L2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="2">
-        <v>46240.52037037037</v>
-      </c>
-      <c r="G3">
-        <v>1722</v>
-      </c>
-      <c r="H3">
-        <v>1722</v>
-      </c>
-      <c r="I3">
-        <v>1722</v>
-      </c>
-      <c r="J3">
-        <v>770</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="2">
-        <v>46240.54273148148</v>
-      </c>
-      <c r="G4">
-        <v>1922</v>
-      </c>
-      <c r="H4">
-        <v>1922</v>
-      </c>
-      <c r="I4">
-        <v>1922</v>
-      </c>
-      <c r="J4">
-        <v>770</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="2">
-        <v>46240.545</v>
-      </c>
-      <c r="G5">
-        <v>4837</v>
-      </c>
-      <c r="H5">
-        <v>4837</v>
-      </c>
-      <c r="I5">
-        <v>4837</v>
-      </c>
-      <c r="J5">
-        <v>770</v>
-      </c>
-      <c r="L5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="2">
-        <v>46240.54693287037</v>
-      </c>
-      <c r="G6">
-        <v>1047</v>
-      </c>
-      <c r="H6">
-        <v>1047</v>
-      </c>
-      <c r="I6">
-        <v>1047</v>
-      </c>
-      <c r="J6">
-        <v>770</v>
-      </c>
-      <c r="L6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="2">
-        <v>46239.97922453703</v>
-      </c>
-      <c r="G7">
-        <v>1683</v>
-      </c>
-      <c r="H7">
-        <v>1683</v>
-      </c>
-      <c r="I7">
-        <v>1683</v>
-      </c>
-      <c r="J7">
-        <v>1308</v>
-      </c>
-      <c r="L7" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="2">
-        <v>46240.96769675926</v>
-      </c>
-      <c r="G8">
-        <v>5000</v>
-      </c>
-      <c r="H8">
-        <v>5000</v>
-      </c>
-      <c r="I8">
-        <v>5000</v>
-      </c>
-      <c r="J8">
-        <v>2630</v>
-      </c>
-      <c r="L8" t="s">
-        <v>27</v>
-      </c>
-      <c r="M8" t="b">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/resources/Z517/spc_sheet_oos_decoration.xlsx
+++ b/resources/Z517/spc_sheet_oos_decoration.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="23">
   <si>
     <t>factory</t>
   </si>
@@ -53,12 +53,45 @@
   </si>
   <si>
     <t>flag</t>
+  </si>
+  <si>
+    <t>ARRAY</t>
+  </si>
+  <si>
+    <t>Z517</t>
+  </si>
+  <si>
+    <t>15620</t>
+  </si>
+  <si>
+    <t>TDSUM</t>
+  </si>
+  <si>
+    <t>L3Z66700C10</t>
+  </si>
+  <si>
+    <t>L3Z66700K04</t>
+  </si>
+  <si>
+    <t>L3Z66700K08</t>
+  </si>
+  <si>
+    <t>L3Z66700K10</t>
+  </si>
+  <si>
+    <t>L3Z66700K16</t>
+  </si>
+  <si>
+    <t>USL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -111,11 +144,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -410,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -454,6 +488,196 @@
         <v>12</v>
       </c>
     </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46245.5975</v>
+      </c>
+      <c r="G2">
+        <v>4350</v>
+      </c>
+      <c r="H2">
+        <v>4350</v>
+      </c>
+      <c r="I2">
+        <v>4350</v>
+      </c>
+      <c r="J2">
+        <v>2630</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="2">
+        <v>46245.88953703704</v>
+      </c>
+      <c r="G3">
+        <v>2722</v>
+      </c>
+      <c r="H3">
+        <v>2722</v>
+      </c>
+      <c r="I3">
+        <v>2722</v>
+      </c>
+      <c r="J3">
+        <v>2630</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46245.91150462963</v>
+      </c>
+      <c r="G4">
+        <v>2989</v>
+      </c>
+      <c r="H4">
+        <v>2989</v>
+      </c>
+      <c r="I4">
+        <v>2989</v>
+      </c>
+      <c r="J4">
+        <v>2630</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2">
+        <v>46245.93844907408</v>
+      </c>
+      <c r="G5">
+        <v>3762</v>
+      </c>
+      <c r="H5">
+        <v>3762</v>
+      </c>
+      <c r="I5">
+        <v>3762</v>
+      </c>
+      <c r="J5">
+        <v>2630</v>
+      </c>
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="2">
+        <v>46245.95363425926</v>
+      </c>
+      <c r="G6">
+        <v>4462</v>
+      </c>
+      <c r="H6">
+        <v>4462</v>
+      </c>
+      <c r="I6">
+        <v>4462</v>
+      </c>
+      <c r="J6">
+        <v>2630</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
